--- a/frontend/kskcolle/public/data/erelijsten/lente.xlsx
+++ b/frontend/kskcolle/public/data/erelijsten/lente.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jvaer\Documents\KSKColle\frontend\kskcolle\public\data\erelijsten\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a822bf281130dcc6/Documenten/Schaken/KSKColle/frontend/kskcolle/public/data/erelijsten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F502E6C2-84CD-4137-A62B-395441FC93AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{F502E6C2-84CD-4137-A62B-395441FC93AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7ABBF68C-7A60-4B73-A4D5-1AC82ED2D7E7}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clubkampioenschap" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="218">
   <si>
     <t>Jaar</t>
   </si>
@@ -633,28 +633,6 @@
   </si>
   <si>
     <t>Marc Cools</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t>2020</t>
-    </r>
   </si>
   <si>
     <t>Evert Heirbaut</t>
@@ -715,7 +693,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -737,13 +715,6 @@
       <family val="3"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FFC00000"/>
       <name val="Courier New"/>
@@ -1082,6 +1053,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -1091,24 +1071,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1116,33 +1078,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1158,6 +1093,42 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1518,7 +1489,7 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="59">
+      <c r="A2" s="47">
         <v>1945</v>
       </c>
       <c r="B2" s="6">
@@ -1537,7 +1508,7 @@
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42"/>
+      <c r="A3" s="39"/>
       <c r="B3" s="10">
         <v>2</v>
       </c>
@@ -1554,7 +1525,7 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="60"/>
+      <c r="A4" s="48"/>
       <c r="B4" s="12">
         <v>3</v>
       </c>
@@ -1571,7 +1542,7 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="47">
+      <c r="A5" s="44">
         <v>1946</v>
       </c>
       <c r="B5" s="6">
@@ -1590,7 +1561,7 @@
       <c r="K5" s="9"/>
     </row>
     <row r="6" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="48"/>
+      <c r="A6" s="45"/>
       <c r="B6" s="10">
         <v>2</v>
       </c>
@@ -1607,7 +1578,7 @@
       <c r="K6" s="9"/>
     </row>
     <row r="7" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="49"/>
+      <c r="A7" s="46"/>
       <c r="B7" s="12">
         <v>3</v>
       </c>
@@ -1624,7 +1595,7 @@
       <c r="K7" s="9"/>
     </row>
     <row r="8" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="41">
+      <c r="A8" s="38">
         <v>1947</v>
       </c>
       <c r="B8" s="6">
@@ -1643,7 +1614,7 @@
       <c r="K8" s="9"/>
     </row>
     <row r="9" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="42"/>
+      <c r="A9" s="39"/>
       <c r="B9" s="10">
         <v>2</v>
       </c>
@@ -1660,7 +1631,7 @@
       <c r="K9" s="9"/>
     </row>
     <row r="10" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="43"/>
+      <c r="A10" s="40"/>
       <c r="B10" s="12">
         <v>3</v>
       </c>
@@ -1677,7 +1648,7 @@
       <c r="K10" s="9"/>
     </row>
     <row r="11" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47">
+      <c r="A11" s="44">
         <v>1948</v>
       </c>
       <c r="B11" s="6">
@@ -1696,7 +1667,7 @@
       <c r="K11" s="9"/>
     </row>
     <row r="12" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="48"/>
+      <c r="A12" s="45"/>
       <c r="B12" s="10">
         <v>2</v>
       </c>
@@ -1713,7 +1684,7 @@
       <c r="K12" s="9"/>
     </row>
     <row r="13" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="49"/>
+      <c r="A13" s="46"/>
       <c r="B13" s="12">
         <v>3</v>
       </c>
@@ -1730,7 +1701,7 @@
       <c r="K13" s="9"/>
     </row>
     <row r="14" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="61">
+      <c r="A14" s="49">
         <v>1949</v>
       </c>
       <c r="B14" s="6">
@@ -1757,7 +1728,7 @@
       <c r="K14" s="9"/>
     </row>
     <row r="15" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="62"/>
+      <c r="A15" s="50"/>
       <c r="B15" s="10">
         <v>2</v>
       </c>
@@ -1782,7 +1753,7 @@
       <c r="K15" s="9"/>
     </row>
     <row r="16" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="63"/>
+      <c r="A16" s="51"/>
       <c r="B16" s="12">
         <v>3</v>
       </c>
@@ -1807,7 +1778,7 @@
       <c r="K16" s="9"/>
     </row>
     <row r="17" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="47">
+      <c r="A17" s="44">
         <v>1950</v>
       </c>
       <c r="B17" s="6">
@@ -1834,7 +1805,7 @@
       <c r="K17" s="9"/>
     </row>
     <row r="18" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="48"/>
+      <c r="A18" s="45"/>
       <c r="B18" s="10">
         <v>2</v>
       </c>
@@ -1859,7 +1830,7 @@
       <c r="K18" s="9"/>
     </row>
     <row r="19" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="49"/>
+      <c r="A19" s="46"/>
       <c r="B19" s="12">
         <v>3</v>
       </c>
@@ -1884,7 +1855,7 @@
       <c r="K19" s="9"/>
     </row>
     <row r="20" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="41">
+      <c r="A20" s="38">
         <v>1951</v>
       </c>
       <c r="B20" s="6">
@@ -1907,7 +1878,7 @@
       <c r="K20" s="9"/>
     </row>
     <row r="21" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="42"/>
+      <c r="A21" s="39"/>
       <c r="B21" s="10">
         <v>2</v>
       </c>
@@ -1928,7 +1899,7 @@
       <c r="K21" s="9"/>
     </row>
     <row r="22" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="43"/>
+      <c r="A22" s="40"/>
       <c r="B22" s="12">
         <v>3</v>
       </c>
@@ -1949,7 +1920,7 @@
       <c r="K22" s="9"/>
     </row>
     <row r="23" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="47">
+      <c r="A23" s="44">
         <v>1952</v>
       </c>
       <c r="B23" s="6">
@@ -1976,7 +1947,7 @@
       <c r="K23" s="9"/>
     </row>
     <row r="24" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="48"/>
+      <c r="A24" s="45"/>
       <c r="B24" s="10">
         <v>2</v>
       </c>
@@ -2001,7 +1972,7 @@
       <c r="K24" s="9"/>
     </row>
     <row r="25" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="49"/>
+      <c r="A25" s="46"/>
       <c r="B25" s="12">
         <v>3</v>
       </c>
@@ -2026,7 +1997,7 @@
       <c r="K25" s="9"/>
     </row>
     <row r="26" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="41">
+      <c r="A26" s="38">
         <v>1953</v>
       </c>
       <c r="B26" s="6">
@@ -2049,7 +2020,7 @@
       <c r="K26" s="9"/>
     </row>
     <row r="27" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="42"/>
+      <c r="A27" s="39"/>
       <c r="B27" s="10">
         <v>2</v>
       </c>
@@ -2070,7 +2041,7 @@
       <c r="K27" s="9"/>
     </row>
     <row r="28" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="43"/>
+      <c r="A28" s="40"/>
       <c r="B28" s="12">
         <v>3</v>
       </c>
@@ -2091,7 +2062,7 @@
       <c r="K28" s="9"/>
     </row>
     <row r="29" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="47">
+      <c r="A29" s="44">
         <v>1954</v>
       </c>
       <c r="B29" s="6">
@@ -2114,7 +2085,7 @@
       <c r="K29" s="9"/>
     </row>
     <row r="30" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="48"/>
+      <c r="A30" s="45"/>
       <c r="B30" s="10">
         <v>2</v>
       </c>
@@ -2135,7 +2106,7 @@
       <c r="K30" s="9"/>
     </row>
     <row r="31" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="49"/>
+      <c r="A31" s="46"/>
       <c r="B31" s="12">
         <v>3</v>
       </c>
@@ -2156,7 +2127,7 @@
       <c r="K31" s="9"/>
     </row>
     <row r="32" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="41">
+      <c r="A32" s="38">
         <v>1955</v>
       </c>
       <c r="B32" s="6">
@@ -2179,7 +2150,7 @@
       <c r="K32" s="9"/>
     </row>
     <row r="33" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="42"/>
+      <c r="A33" s="39"/>
       <c r="B33" s="10">
         <v>2</v>
       </c>
@@ -2200,7 +2171,7 @@
       <c r="K33" s="9"/>
     </row>
     <row r="34" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="43"/>
+      <c r="A34" s="40"/>
       <c r="B34" s="12">
         <v>3</v>
       </c>
@@ -2221,7 +2192,7 @@
       <c r="K34" s="9"/>
     </row>
     <row r="35" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="47">
+      <c r="A35" s="44">
         <v>1956</v>
       </c>
       <c r="B35" s="6">
@@ -2244,7 +2215,7 @@
       <c r="K35" s="9"/>
     </row>
     <row r="36" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="48"/>
+      <c r="A36" s="45"/>
       <c r="B36" s="10">
         <v>2</v>
       </c>
@@ -2265,7 +2236,7 @@
       <c r="K36" s="9"/>
     </row>
     <row r="37" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="49"/>
+      <c r="A37" s="46"/>
       <c r="B37" s="12">
         <v>3</v>
       </c>
@@ -2286,7 +2257,7 @@
       <c r="K37" s="9"/>
     </row>
     <row r="38" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="41">
+      <c r="A38" s="38">
         <v>1957</v>
       </c>
       <c r="B38" s="6">
@@ -2305,7 +2276,7 @@
       <c r="K38" s="9"/>
     </row>
     <row r="39" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="42"/>
+      <c r="A39" s="39"/>
       <c r="B39" s="10">
         <v>2</v>
       </c>
@@ -2322,7 +2293,7 @@
       <c r="K39" s="9"/>
     </row>
     <row r="40" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="43"/>
+      <c r="A40" s="40"/>
       <c r="B40" s="12">
         <v>3</v>
       </c>
@@ -2339,7 +2310,7 @@
       <c r="K40" s="9"/>
     </row>
     <row r="41" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="47">
+      <c r="A41" s="44">
         <v>1958</v>
       </c>
       <c r="B41" s="6">
@@ -2358,7 +2329,7 @@
       <c r="K41" s="9"/>
     </row>
     <row r="42" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="48"/>
+      <c r="A42" s="45"/>
       <c r="B42" s="10">
         <v>2</v>
       </c>
@@ -2375,7 +2346,7 @@
       <c r="K42" s="9"/>
     </row>
     <row r="43" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="49"/>
+      <c r="A43" s="46"/>
       <c r="B43" s="12">
         <v>3</v>
       </c>
@@ -2392,7 +2363,7 @@
       <c r="K43" s="9"/>
     </row>
     <row r="44" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="41">
+      <c r="A44" s="38">
         <v>1959</v>
       </c>
       <c r="B44" s="6">
@@ -2415,7 +2386,7 @@
       <c r="K44" s="9"/>
     </row>
     <row r="45" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="42"/>
+      <c r="A45" s="39"/>
       <c r="B45" s="10">
         <v>2</v>
       </c>
@@ -2436,7 +2407,7 @@
       <c r="K45" s="9"/>
     </row>
     <row r="46" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="43"/>
+      <c r="A46" s="40"/>
       <c r="B46" s="12">
         <v>3</v>
       </c>
@@ -2457,7 +2428,7 @@
       <c r="K46" s="9"/>
     </row>
     <row r="47" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="47">
+      <c r="A47" s="44">
         <v>1960</v>
       </c>
       <c r="B47" s="6">
@@ -2480,7 +2451,7 @@
       <c r="K47" s="9"/>
     </row>
     <row r="48" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="48"/>
+      <c r="A48" s="45"/>
       <c r="B48" s="10">
         <v>2</v>
       </c>
@@ -2501,7 +2472,7 @@
       <c r="K48" s="9"/>
     </row>
     <row r="49" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="49"/>
+      <c r="A49" s="46"/>
       <c r="B49" s="12">
         <v>3</v>
       </c>
@@ -2522,7 +2493,7 @@
       <c r="K49" s="9"/>
     </row>
     <row r="50" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="41">
+      <c r="A50" s="38">
         <v>1961</v>
       </c>
       <c r="B50" s="6">
@@ -2545,7 +2516,7 @@
       <c r="K50" s="9"/>
     </row>
     <row r="51" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="42"/>
+      <c r="A51" s="39"/>
       <c r="B51" s="10">
         <v>2</v>
       </c>
@@ -2566,7 +2537,7 @@
       <c r="K51" s="9"/>
     </row>
     <row r="52" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="43"/>
+      <c r="A52" s="40"/>
       <c r="B52" s="12">
         <v>3</v>
       </c>
@@ -2587,7 +2558,7 @@
       <c r="K52" s="9"/>
     </row>
     <row r="53" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="47">
+      <c r="A53" s="44">
         <v>1962</v>
       </c>
       <c r="B53" s="6">
@@ -2610,7 +2581,7 @@
       <c r="K53" s="9"/>
     </row>
     <row r="54" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="48"/>
+      <c r="A54" s="45"/>
       <c r="B54" s="10">
         <v>2</v>
       </c>
@@ -2631,7 +2602,7 @@
       <c r="K54" s="9"/>
     </row>
     <row r="55" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="49"/>
+      <c r="A55" s="46"/>
       <c r="B55" s="12">
         <v>3</v>
       </c>
@@ -2652,7 +2623,7 @@
       <c r="K55" s="9"/>
     </row>
     <row r="56" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="41">
+      <c r="A56" s="38">
         <v>1963</v>
       </c>
       <c r="B56" s="6">
@@ -2675,7 +2646,7 @@
       <c r="K56" s="9"/>
     </row>
     <row r="57" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="42"/>
+      <c r="A57" s="39"/>
       <c r="B57" s="10">
         <v>2</v>
       </c>
@@ -2696,7 +2667,7 @@
       <c r="K57" s="9"/>
     </row>
     <row r="58" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="43"/>
+      <c r="A58" s="40"/>
       <c r="B58" s="12">
         <v>3</v>
       </c>
@@ -2717,7 +2688,7 @@
       <c r="K58" s="9"/>
     </row>
     <row r="59" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="47">
+      <c r="A59" s="44">
         <v>1964</v>
       </c>
       <c r="B59" s="6">
@@ -2740,7 +2711,7 @@
       <c r="K59" s="9"/>
     </row>
     <row r="60" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="48"/>
+      <c r="A60" s="45"/>
       <c r="B60" s="10">
         <v>2</v>
       </c>
@@ -2761,7 +2732,7 @@
       <c r="K60" s="9"/>
     </row>
     <row r="61" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="49"/>
+      <c r="A61" s="46"/>
       <c r="B61" s="12">
         <v>3</v>
       </c>
@@ -2782,7 +2753,7 @@
       <c r="K61" s="9"/>
     </row>
     <row r="62" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="41">
+      <c r="A62" s="38">
         <v>1965</v>
       </c>
       <c r="B62" s="6">
@@ -2805,7 +2776,7 @@
       <c r="K62" s="9"/>
     </row>
     <row r="63" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="42"/>
+      <c r="A63" s="39"/>
       <c r="B63" s="10">
         <v>2</v>
       </c>
@@ -2826,7 +2797,7 @@
       <c r="K63" s="9"/>
     </row>
     <row r="64" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="43"/>
+      <c r="A64" s="40"/>
       <c r="B64" s="12">
         <v>3</v>
       </c>
@@ -2847,7 +2818,7 @@
       <c r="K64" s="9"/>
     </row>
     <row r="65" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="47">
+      <c r="A65" s="44">
         <v>1966</v>
       </c>
       <c r="B65" s="6">
@@ -2870,7 +2841,7 @@
       <c r="K65" s="9"/>
     </row>
     <row r="66" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="48"/>
+      <c r="A66" s="45"/>
       <c r="B66" s="10">
         <v>2</v>
       </c>
@@ -2891,7 +2862,7 @@
       <c r="K66" s="9"/>
     </row>
     <row r="67" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="49"/>
+      <c r="A67" s="46"/>
       <c r="B67" s="12">
         <v>3</v>
       </c>
@@ -2912,7 +2883,7 @@
       <c r="K67" s="9"/>
     </row>
     <row r="68" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="41">
+      <c r="A68" s="38">
         <v>1967</v>
       </c>
       <c r="B68" s="6">
@@ -2935,7 +2906,7 @@
       <c r="K68" s="9"/>
     </row>
     <row r="69" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="42"/>
+      <c r="A69" s="39"/>
       <c r="B69" s="10">
         <v>2</v>
       </c>
@@ -2956,7 +2927,7 @@
       <c r="K69" s="9"/>
     </row>
     <row r="70" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="43"/>
+      <c r="A70" s="40"/>
       <c r="B70" s="12">
         <v>3</v>
       </c>
@@ -2977,7 +2948,7 @@
       <c r="K70" s="9"/>
     </row>
     <row r="71" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="47">
+      <c r="A71" s="44">
         <v>1968</v>
       </c>
       <c r="B71" s="6">
@@ -3000,7 +2971,7 @@
       <c r="K71" s="9"/>
     </row>
     <row r="72" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="48"/>
+      <c r="A72" s="45"/>
       <c r="B72" s="10">
         <v>2</v>
       </c>
@@ -3021,7 +2992,7 @@
       <c r="K72" s="9"/>
     </row>
     <row r="73" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="49"/>
+      <c r="A73" s="46"/>
       <c r="B73" s="12">
         <v>3</v>
       </c>
@@ -3042,7 +3013,7 @@
       <c r="K73" s="9"/>
     </row>
     <row r="74" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="41">
+      <c r="A74" s="38">
         <v>1969</v>
       </c>
       <c r="B74" s="6">
@@ -3065,7 +3036,7 @@
       <c r="K74" s="9"/>
     </row>
     <row r="75" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="42"/>
+      <c r="A75" s="39"/>
       <c r="B75" s="10">
         <v>2</v>
       </c>
@@ -3086,7 +3057,7 @@
       <c r="K75" s="9"/>
     </row>
     <row r="76" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="43"/>
+      <c r="A76" s="40"/>
       <c r="B76" s="12">
         <v>3</v>
       </c>
@@ -3107,7 +3078,7 @@
       <c r="K76" s="9"/>
     </row>
     <row r="77" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="47">
+      <c r="A77" s="44">
         <v>1970</v>
       </c>
       <c r="B77" s="6">
@@ -3130,7 +3101,7 @@
       <c r="K77" s="9"/>
     </row>
     <row r="78" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="48"/>
+      <c r="A78" s="45"/>
       <c r="B78" s="10">
         <v>2</v>
       </c>
@@ -3151,7 +3122,7 @@
       <c r="K78" s="9"/>
     </row>
     <row r="79" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="49"/>
+      <c r="A79" s="46"/>
       <c r="B79" s="12">
         <v>3</v>
       </c>
@@ -3172,7 +3143,7 @@
       <c r="K79" s="9"/>
     </row>
     <row r="80" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="41">
+      <c r="A80" s="38">
         <v>1971</v>
       </c>
       <c r="B80" s="6">
@@ -3199,7 +3170,7 @@
       <c r="K80" s="9"/>
     </row>
     <row r="81" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="42"/>
+      <c r="A81" s="39"/>
       <c r="B81" s="10">
         <v>2</v>
       </c>
@@ -3224,7 +3195,7 @@
       <c r="K81" s="9"/>
     </row>
     <row r="82" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="43"/>
+      <c r="A82" s="40"/>
       <c r="B82" s="12">
         <v>3</v>
       </c>
@@ -3249,7 +3220,7 @@
       <c r="K82" s="9"/>
     </row>
     <row r="83" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="47">
+      <c r="A83" s="44">
         <v>1972</v>
       </c>
       <c r="B83" s="6">
@@ -3276,7 +3247,7 @@
       <c r="K83" s="9"/>
     </row>
     <row r="84" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="48"/>
+      <c r="A84" s="45"/>
       <c r="B84" s="10">
         <v>2</v>
       </c>
@@ -3301,7 +3272,7 @@
       <c r="K84" s="9"/>
     </row>
     <row r="85" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="49"/>
+      <c r="A85" s="46"/>
       <c r="B85" s="12">
         <v>3</v>
       </c>
@@ -3326,7 +3297,7 @@
       <c r="K85" s="9"/>
     </row>
     <row r="86" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="41">
+      <c r="A86" s="38">
         <v>1973</v>
       </c>
       <c r="B86" s="6">
@@ -3357,7 +3328,7 @@
       <c r="K86" s="9"/>
     </row>
     <row r="87" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="42"/>
+      <c r="A87" s="39"/>
       <c r="B87" s="10">
         <v>2</v>
       </c>
@@ -3386,7 +3357,7 @@
       <c r="K87" s="9"/>
     </row>
     <row r="88" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="43"/>
+      <c r="A88" s="40"/>
       <c r="B88" s="12">
         <v>3</v>
       </c>
@@ -3415,7 +3386,7 @@
       <c r="K88" s="9"/>
     </row>
     <row r="89" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="47">
+      <c r="A89" s="44">
         <v>1974</v>
       </c>
       <c r="B89" s="6">
@@ -3442,7 +3413,7 @@
       <c r="K89" s="9"/>
     </row>
     <row r="90" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="48"/>
+      <c r="A90" s="45"/>
       <c r="B90" s="10">
         <v>2</v>
       </c>
@@ -3467,7 +3438,7 @@
       <c r="K90" s="9"/>
     </row>
     <row r="91" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="49"/>
+      <c r="A91" s="46"/>
       <c r="B91" s="12">
         <v>3</v>
       </c>
@@ -3492,7 +3463,7 @@
       <c r="K91" s="9"/>
     </row>
     <row r="92" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="41">
+      <c r="A92" s="38">
         <v>1975</v>
       </c>
       <c r="B92" s="6">
@@ -3519,7 +3490,7 @@
       <c r="K92" s="9"/>
     </row>
     <row r="93" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="42"/>
+      <c r="A93" s="39"/>
       <c r="B93" s="10">
         <v>2</v>
       </c>
@@ -3544,7 +3515,7 @@
       <c r="K93" s="9"/>
     </row>
     <row r="94" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="43"/>
+      <c r="A94" s="40"/>
       <c r="B94" s="12">
         <v>3</v>
       </c>
@@ -3569,7 +3540,7 @@
       <c r="K94" s="9"/>
     </row>
     <row r="95" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="47">
+      <c r="A95" s="44">
         <v>1976</v>
       </c>
       <c r="B95" s="6">
@@ -3596,7 +3567,7 @@
       <c r="K95" s="9"/>
     </row>
     <row r="96" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="48"/>
+      <c r="A96" s="45"/>
       <c r="B96" s="10">
         <v>2</v>
       </c>
@@ -3621,7 +3592,7 @@
       <c r="K96" s="9"/>
     </row>
     <row r="97" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="49"/>
+      <c r="A97" s="46"/>
       <c r="B97" s="12">
         <v>3</v>
       </c>
@@ -3646,7 +3617,7 @@
       <c r="K97" s="9"/>
     </row>
     <row r="98" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="41">
+      <c r="A98" s="38">
         <v>1977</v>
       </c>
       <c r="B98" s="6">
@@ -3673,7 +3644,7 @@
       <c r="K98" s="9"/>
     </row>
     <row r="99" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="42"/>
+      <c r="A99" s="39"/>
       <c r="B99" s="10">
         <v>2</v>
       </c>
@@ -3698,7 +3669,7 @@
       <c r="K99" s="9"/>
     </row>
     <row r="100" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="43"/>
+      <c r="A100" s="40"/>
       <c r="B100" s="12">
         <v>3</v>
       </c>
@@ -3723,7 +3694,7 @@
       <c r="K100" s="9"/>
     </row>
     <row r="101" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="47">
+      <c r="A101" s="44">
         <v>1978</v>
       </c>
       <c r="B101" s="6">
@@ -3750,7 +3721,7 @@
       <c r="K101" s="9"/>
     </row>
     <row r="102" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="48"/>
+      <c r="A102" s="45"/>
       <c r="B102" s="10">
         <v>2</v>
       </c>
@@ -3775,7 +3746,7 @@
       <c r="K102" s="9"/>
     </row>
     <row r="103" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="49"/>
+      <c r="A103" s="46"/>
       <c r="B103" s="12">
         <v>3</v>
       </c>
@@ -3800,7 +3771,7 @@
       <c r="K103" s="9"/>
     </row>
     <row r="104" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="41">
+      <c r="A104" s="38">
         <v>1979</v>
       </c>
       <c r="B104" s="6">
@@ -3827,7 +3798,7 @@
       <c r="K104" s="9"/>
     </row>
     <row r="105" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="42"/>
+      <c r="A105" s="39"/>
       <c r="B105" s="10">
         <v>2</v>
       </c>
@@ -3852,7 +3823,7 @@
       <c r="K105" s="9"/>
     </row>
     <row r="106" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="43"/>
+      <c r="A106" s="40"/>
       <c r="B106" s="12">
         <v>3</v>
       </c>
@@ -3877,7 +3848,7 @@
       <c r="K106" s="9"/>
     </row>
     <row r="107" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="47">
+      <c r="A107" s="44">
         <v>1980</v>
       </c>
       <c r="B107" s="6">
@@ -3904,7 +3875,7 @@
       <c r="K107" s="9"/>
     </row>
     <row r="108" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="48"/>
+      <c r="A108" s="45"/>
       <c r="B108" s="10">
         <v>2</v>
       </c>
@@ -3929,7 +3900,7 @@
       <c r="K108" s="9"/>
     </row>
     <row r="109" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="49"/>
+      <c r="A109" s="46"/>
       <c r="B109" s="12">
         <v>3</v>
       </c>
@@ -3954,7 +3925,7 @@
       <c r="K109" s="9"/>
     </row>
     <row r="110" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="41">
+      <c r="A110" s="38">
         <v>1981</v>
       </c>
       <c r="B110" s="6">
@@ -3981,7 +3952,7 @@
       <c r="K110" s="9"/>
     </row>
     <row r="111" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="42"/>
+      <c r="A111" s="39"/>
       <c r="B111" s="10">
         <v>2</v>
       </c>
@@ -4006,7 +3977,7 @@
       <c r="K111" s="9"/>
     </row>
     <row r="112" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="43"/>
+      <c r="A112" s="40"/>
       <c r="B112" s="12">
         <v>3</v>
       </c>
@@ -4031,7 +4002,7 @@
       <c r="K112" s="9"/>
     </row>
     <row r="113" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="47">
+      <c r="A113" s="44">
         <v>1982</v>
       </c>
       <c r="B113" s="6">
@@ -4058,7 +4029,7 @@
       <c r="K113" s="9"/>
     </row>
     <row r="114" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="48"/>
+      <c r="A114" s="45"/>
       <c r="B114" s="10">
         <v>2</v>
       </c>
@@ -4083,7 +4054,7 @@
       <c r="K114" s="9"/>
     </row>
     <row r="115" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="49"/>
+      <c r="A115" s="46"/>
       <c r="B115" s="12">
         <v>3</v>
       </c>
@@ -4108,7 +4079,7 @@
       <c r="K115" s="9"/>
     </row>
     <row r="116" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="41">
+      <c r="A116" s="38">
         <v>1983</v>
       </c>
       <c r="B116" s="6">
@@ -4135,7 +4106,7 @@
       <c r="K116" s="9"/>
     </row>
     <row r="117" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="42"/>
+      <c r="A117" s="39"/>
       <c r="B117" s="10">
         <v>2</v>
       </c>
@@ -4160,7 +4131,7 @@
       <c r="K117" s="9"/>
     </row>
     <row r="118" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="43"/>
+      <c r="A118" s="40"/>
       <c r="B118" s="12">
         <v>3</v>
       </c>
@@ -4185,7 +4156,7 @@
       <c r="K118" s="9"/>
     </row>
     <row r="119" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="47">
+      <c r="A119" s="44">
         <v>1984</v>
       </c>
       <c r="B119" s="6">
@@ -4212,7 +4183,7 @@
       <c r="K119" s="9"/>
     </row>
     <row r="120" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="48"/>
+      <c r="A120" s="45"/>
       <c r="B120" s="10">
         <v>2</v>
       </c>
@@ -4237,7 +4208,7 @@
       <c r="K120" s="9"/>
     </row>
     <row r="121" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="49"/>
+      <c r="A121" s="46"/>
       <c r="B121" s="12">
         <v>3</v>
       </c>
@@ -4262,7 +4233,7 @@
       <c r="K121" s="9"/>
     </row>
     <row r="122" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="41">
+      <c r="A122" s="38">
         <v>1985</v>
       </c>
       <c r="B122" s="6">
@@ -4289,7 +4260,7 @@
       <c r="K122" s="9"/>
     </row>
     <row r="123" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="42"/>
+      <c r="A123" s="39"/>
       <c r="B123" s="10">
         <v>2</v>
       </c>
@@ -4314,7 +4285,7 @@
       <c r="K123" s="9"/>
     </row>
     <row r="124" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="43"/>
+      <c r="A124" s="40"/>
       <c r="B124" s="12">
         <v>3</v>
       </c>
@@ -4339,7 +4310,7 @@
       <c r="K124" s="9"/>
     </row>
     <row r="125" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="47">
+      <c r="A125" s="44">
         <v>1986</v>
       </c>
       <c r="B125" s="6">
@@ -4366,7 +4337,7 @@
       <c r="K125" s="9"/>
     </row>
     <row r="126" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="48"/>
+      <c r="A126" s="45"/>
       <c r="B126" s="10">
         <v>2</v>
       </c>
@@ -4391,7 +4362,7 @@
       <c r="K126" s="9"/>
     </row>
     <row r="127" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="49"/>
+      <c r="A127" s="46"/>
       <c r="B127" s="12">
         <v>3</v>
       </c>
@@ -4416,7 +4387,7 @@
       <c r="K127" s="9"/>
     </row>
     <row r="128" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="41">
+      <c r="A128" s="38">
         <v>1987</v>
       </c>
       <c r="B128" s="6">
@@ -4443,7 +4414,7 @@
       <c r="K128" s="9"/>
     </row>
     <row r="129" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="42"/>
+      <c r="A129" s="39"/>
       <c r="B129" s="10">
         <v>2</v>
       </c>
@@ -4468,7 +4439,7 @@
       <c r="K129" s="9"/>
     </row>
     <row r="130" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="43"/>
+      <c r="A130" s="40"/>
       <c r="B130" s="12">
         <v>3</v>
       </c>
@@ -4493,7 +4464,7 @@
       <c r="K130" s="9"/>
     </row>
     <row r="131" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="47">
+      <c r="A131" s="44">
         <v>1988</v>
       </c>
       <c r="B131" s="6">
@@ -4520,7 +4491,7 @@
       <c r="K131" s="9"/>
     </row>
     <row r="132" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="48"/>
+      <c r="A132" s="45"/>
       <c r="B132" s="10">
         <v>2</v>
       </c>
@@ -4545,7 +4516,7 @@
       <c r="K132" s="9"/>
     </row>
     <row r="133" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="49"/>
+      <c r="A133" s="46"/>
       <c r="B133" s="12">
         <v>3</v>
       </c>
@@ -4570,7 +4541,7 @@
       <c r="K133" s="9"/>
     </row>
     <row r="134" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="41">
+      <c r="A134" s="38">
         <v>1989</v>
       </c>
       <c r="B134" s="6">
@@ -4601,7 +4572,7 @@
       <c r="K134" s="9"/>
     </row>
     <row r="135" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="42"/>
+      <c r="A135" s="39"/>
       <c r="B135" s="10">
         <v>2</v>
       </c>
@@ -4630,7 +4601,7 @@
       <c r="K135" s="9"/>
     </row>
     <row r="136" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="43"/>
+      <c r="A136" s="40"/>
       <c r="B136" s="12">
         <v>3</v>
       </c>
@@ -4659,7 +4630,7 @@
       <c r="K136" s="9"/>
     </row>
     <row r="137" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="47">
+      <c r="A137" s="44">
         <v>1990</v>
       </c>
       <c r="B137" s="6">
@@ -4690,7 +4661,7 @@
       <c r="K137" s="9"/>
     </row>
     <row r="138" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="48"/>
+      <c r="A138" s="45"/>
       <c r="B138" s="10">
         <v>2</v>
       </c>
@@ -4719,7 +4690,7 @@
       <c r="K138" s="9"/>
     </row>
     <row r="139" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="49"/>
+      <c r="A139" s="46"/>
       <c r="B139" s="12">
         <v>3</v>
       </c>
@@ -4748,7 +4719,7 @@
       <c r="K139" s="9"/>
     </row>
     <row r="140" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="50">
+      <c r="A140" s="52">
         <v>1991</v>
       </c>
       <c r="B140" s="6">
@@ -4779,7 +4750,7 @@
       <c r="K140" s="9"/>
     </row>
     <row r="141" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="51"/>
+      <c r="A141" s="53"/>
       <c r="B141" s="10">
         <v>2</v>
       </c>
@@ -4808,7 +4779,7 @@
       <c r="K141" s="9"/>
     </row>
     <row r="142" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="52"/>
+      <c r="A142" s="54"/>
       <c r="B142" s="12">
         <v>3</v>
       </c>
@@ -4837,7 +4808,7 @@
       <c r="K142" s="9"/>
     </row>
     <row r="143" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="47">
+      <c r="A143" s="44">
         <v>1992</v>
       </c>
       <c r="B143" s="6">
@@ -4868,7 +4839,7 @@
       <c r="K143" s="26"/>
     </row>
     <row r="144" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="48"/>
+      <c r="A144" s="45"/>
       <c r="B144" s="10">
         <v>2</v>
       </c>
@@ -4897,7 +4868,7 @@
       <c r="K144" s="26"/>
     </row>
     <row r="145" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="49"/>
+      <c r="A145" s="46"/>
       <c r="B145" s="12">
         <v>3</v>
       </c>
@@ -4926,7 +4897,7 @@
       <c r="K145" s="26"/>
     </row>
     <row r="146" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="44">
+      <c r="A146" s="55">
         <v>1993</v>
       </c>
       <c r="B146" s="6">
@@ -4957,7 +4928,7 @@
       <c r="K146" s="26"/>
     </row>
     <row r="147" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="45"/>
+      <c r="A147" s="56"/>
       <c r="B147" s="10">
         <v>2</v>
       </c>
@@ -4986,7 +4957,7 @@
       <c r="K147" s="26"/>
     </row>
     <row r="148" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="46"/>
+      <c r="A148" s="57"/>
       <c r="B148" s="12">
         <v>3</v>
       </c>
@@ -5015,7 +4986,7 @@
       <c r="K148" s="26"/>
     </row>
     <row r="149" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="47">
+      <c r="A149" s="44">
         <v>1994</v>
       </c>
       <c r="B149" s="6">
@@ -5046,7 +5017,7 @@
       <c r="K149" s="26"/>
     </row>
     <row r="150" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="48"/>
+      <c r="A150" s="45"/>
       <c r="B150" s="10">
         <v>2</v>
       </c>
@@ -5075,7 +5046,7 @@
       <c r="K150" s="26"/>
     </row>
     <row r="151" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="49"/>
+      <c r="A151" s="46"/>
       <c r="B151" s="12">
         <v>3</v>
       </c>
@@ -5104,7 +5075,7 @@
       <c r="K151" s="26"/>
     </row>
     <row r="152" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="44">
+      <c r="A152" s="55">
         <v>1995</v>
       </c>
       <c r="B152" s="6">
@@ -5135,7 +5106,7 @@
       <c r="K152" s="26"/>
     </row>
     <row r="153" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="45"/>
+      <c r="A153" s="56"/>
       <c r="B153" s="10">
         <v>2</v>
       </c>
@@ -5164,7 +5135,7 @@
       <c r="K153" s="26"/>
     </row>
     <row r="154" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="46"/>
+      <c r="A154" s="57"/>
       <c r="B154" s="12">
         <v>3</v>
       </c>
@@ -5193,7 +5164,7 @@
       <c r="K154" s="26"/>
     </row>
     <row r="155" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="47">
+      <c r="A155" s="44">
         <v>1996</v>
       </c>
       <c r="B155" s="6">
@@ -5224,7 +5195,7 @@
       <c r="K155" s="26"/>
     </row>
     <row r="156" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="48"/>
+      <c r="A156" s="45"/>
       <c r="B156" s="10">
         <v>2</v>
       </c>
@@ -5253,7 +5224,7 @@
       <c r="K156" s="26"/>
     </row>
     <row r="157" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="49"/>
+      <c r="A157" s="46"/>
       <c r="B157" s="12">
         <v>3</v>
       </c>
@@ -5282,7 +5253,7 @@
       <c r="K157" s="26"/>
     </row>
     <row r="158" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="44">
+      <c r="A158" s="55">
         <v>1997</v>
       </c>
       <c r="B158" s="6">
@@ -5313,7 +5284,7 @@
       <c r="K158" s="26"/>
     </row>
     <row r="159" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="45"/>
+      <c r="A159" s="56"/>
       <c r="B159" s="10">
         <v>2</v>
       </c>
@@ -5342,7 +5313,7 @@
       <c r="K159" s="26"/>
     </row>
     <row r="160" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="46"/>
+      <c r="A160" s="57"/>
       <c r="B160" s="12">
         <v>3</v>
       </c>
@@ -5371,7 +5342,7 @@
       <c r="K160" s="26"/>
     </row>
     <row r="161" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="47">
+      <c r="A161" s="44">
         <v>1998</v>
       </c>
       <c r="B161" s="6">
@@ -5396,13 +5367,13 @@
         <v>1</v>
       </c>
       <c r="I161" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J161" s="25"/>
       <c r="K161" s="26"/>
     </row>
     <row r="162" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="48"/>
+      <c r="A162" s="45"/>
       <c r="B162" s="10">
         <v>2</v>
       </c>
@@ -5431,7 +5402,7 @@
       <c r="K162" s="26"/>
     </row>
     <row r="163" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="49"/>
+      <c r="A163" s="46"/>
       <c r="B163" s="12">
         <v>3</v>
       </c>
@@ -5460,7 +5431,7 @@
       <c r="K163" s="26"/>
     </row>
     <row r="164" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="44">
+      <c r="A164" s="55">
         <v>1999</v>
       </c>
       <c r="B164" s="6">
@@ -5479,7 +5450,7 @@
         <v>1</v>
       </c>
       <c r="G164" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H164" s="8"/>
       <c r="I164" s="16"/>
@@ -5487,7 +5458,7 @@
       <c r="K164" s="26"/>
     </row>
     <row r="165" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="45"/>
+      <c r="A165" s="56"/>
       <c r="B165" s="10">
         <v>2</v>
       </c>
@@ -5512,7 +5483,7 @@
       <c r="K165" s="26"/>
     </row>
     <row r="166" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="46"/>
+      <c r="A166" s="57"/>
       <c r="B166" s="12">
         <v>3</v>
       </c>
@@ -5537,7 +5508,7 @@
       <c r="K166" s="26"/>
     </row>
     <row r="167" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="47">
+      <c r="A167" s="44">
         <v>2000</v>
       </c>
       <c r="B167" s="6">
@@ -5564,7 +5535,7 @@
       <c r="K167" s="26"/>
     </row>
     <row r="168" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="48"/>
+      <c r="A168" s="45"/>
       <c r="B168" s="10">
         <v>2</v>
       </c>
@@ -5589,7 +5560,7 @@
       <c r="K168" s="26"/>
     </row>
     <row r="169" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="49"/>
+      <c r="A169" s="46"/>
       <c r="B169" s="12">
         <v>3</v>
       </c>
@@ -5600,7 +5571,7 @@
         <v>3</v>
       </c>
       <c r="E169" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F169" s="12">
         <v>3</v>
@@ -5614,7 +5585,7 @@
       <c r="K169" s="26"/>
     </row>
     <row r="170" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="44">
+      <c r="A170" s="55">
         <v>2001</v>
       </c>
       <c r="B170" s="6">
@@ -5641,7 +5612,7 @@
       <c r="K170" s="26"/>
     </row>
     <row r="171" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="45"/>
+      <c r="A171" s="56"/>
       <c r="B171" s="10">
         <v>2</v>
       </c>
@@ -5666,7 +5637,7 @@
       <c r="K171" s="26"/>
     </row>
     <row r="172" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="46"/>
+      <c r="A172" s="57"/>
       <c r="B172" s="12">
         <v>3</v>
       </c>
@@ -5691,7 +5662,7 @@
       <c r="K172" s="26"/>
     </row>
     <row r="173" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="47">
+      <c r="A173" s="44">
         <v>2002</v>
       </c>
       <c r="B173" s="6">
@@ -5718,7 +5689,7 @@
       <c r="K173" s="26"/>
     </row>
     <row r="174" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="48"/>
+      <c r="A174" s="45"/>
       <c r="B174" s="10">
         <v>2</v>
       </c>
@@ -5743,7 +5714,7 @@
       <c r="K174" s="26"/>
     </row>
     <row r="175" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="49"/>
+      <c r="A175" s="46"/>
       <c r="B175" s="12">
         <v>3</v>
       </c>
@@ -5768,7 +5739,7 @@
       <c r="K175" s="26"/>
     </row>
     <row r="176" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="44">
+      <c r="A176" s="55">
         <v>2003</v>
       </c>
       <c r="B176" s="6">
@@ -5795,7 +5766,7 @@
       <c r="K176" s="26"/>
     </row>
     <row r="177" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="45"/>
+      <c r="A177" s="56"/>
       <c r="B177" s="10">
         <v>2</v>
       </c>
@@ -5820,7 +5791,7 @@
       <c r="K177" s="26"/>
     </row>
     <row r="178" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="46"/>
+      <c r="A178" s="57"/>
       <c r="B178" s="12">
         <v>3</v>
       </c>
@@ -5845,7 +5816,7 @@
       <c r="K178" s="26"/>
     </row>
     <row r="179" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="47">
+      <c r="A179" s="44">
         <v>2004</v>
       </c>
       <c r="B179" s="6">
@@ -5872,7 +5843,7 @@
       <c r="K179" s="26"/>
     </row>
     <row r="180" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="48"/>
+      <c r="A180" s="45"/>
       <c r="B180" s="10">
         <v>2</v>
       </c>
@@ -5897,7 +5868,7 @@
       <c r="K180" s="26"/>
     </row>
     <row r="181" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="49"/>
+      <c r="A181" s="46"/>
       <c r="B181" s="12">
         <v>3</v>
       </c>
@@ -5922,7 +5893,7 @@
       <c r="K181" s="26"/>
     </row>
     <row r="182" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="44">
+      <c r="A182" s="55">
         <v>2005</v>
       </c>
       <c r="B182" s="6">
@@ -5949,7 +5920,7 @@
       <c r="K182" s="26"/>
     </row>
     <row r="183" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="45"/>
+      <c r="A183" s="56"/>
       <c r="B183" s="10">
         <v>2</v>
       </c>
@@ -5974,7 +5945,7 @@
       <c r="K183" s="26"/>
     </row>
     <row r="184" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="46"/>
+      <c r="A184" s="57"/>
       <c r="B184" s="12">
         <v>3</v>
       </c>
@@ -5999,7 +5970,7 @@
       <c r="K184" s="26"/>
     </row>
     <row r="185" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="47">
+      <c r="A185" s="44">
         <v>2006</v>
       </c>
       <c r="B185" s="6">
@@ -6030,7 +6001,7 @@
       <c r="K185" s="26"/>
     </row>
     <row r="186" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="48"/>
+      <c r="A186" s="45"/>
       <c r="B186" s="10">
         <v>2</v>
       </c>
@@ -6059,7 +6030,7 @@
       <c r="K186" s="26"/>
     </row>
     <row r="187" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="49"/>
+      <c r="A187" s="46"/>
       <c r="B187" s="12">
         <v>3</v>
       </c>
@@ -6088,7 +6059,7 @@
       <c r="K187" s="26"/>
     </row>
     <row r="188" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="44">
+      <c r="A188" s="55">
         <v>2007</v>
       </c>
       <c r="B188" s="6">
@@ -6119,7 +6090,7 @@
       <c r="K188" s="26"/>
     </row>
     <row r="189" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="45"/>
+      <c r="A189" s="56"/>
       <c r="B189" s="10">
         <v>2</v>
       </c>
@@ -6148,7 +6119,7 @@
       <c r="K189" s="26"/>
     </row>
     <row r="190" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="46"/>
+      <c r="A190" s="57"/>
       <c r="B190" s="12">
         <v>3</v>
       </c>
@@ -6177,7 +6148,7 @@
       <c r="K190" s="26"/>
     </row>
     <row r="191" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="47">
+      <c r="A191" s="44">
         <v>2008</v>
       </c>
       <c r="B191" s="6">
@@ -6204,7 +6175,7 @@
       <c r="K191" s="26"/>
     </row>
     <row r="192" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="48"/>
+      <c r="A192" s="45"/>
       <c r="B192" s="10">
         <v>2</v>
       </c>
@@ -6229,7 +6200,7 @@
       <c r="K192" s="26"/>
     </row>
     <row r="193" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="49"/>
+      <c r="A193" s="46"/>
       <c r="B193" s="12">
         <v>3</v>
       </c>
@@ -6254,7 +6225,7 @@
       <c r="K193" s="26"/>
     </row>
     <row r="194" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="44">
+      <c r="A194" s="55">
         <v>2009</v>
       </c>
       <c r="B194" s="6">
@@ -6285,7 +6256,7 @@
       <c r="K194" s="26"/>
     </row>
     <row r="195" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="45"/>
+      <c r="A195" s="56"/>
       <c r="B195" s="10">
         <v>2</v>
       </c>
@@ -6314,7 +6285,7 @@
       <c r="K195" s="26"/>
     </row>
     <row r="196" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="46"/>
+      <c r="A196" s="57"/>
       <c r="B196" s="12">
         <v>3</v>
       </c>
@@ -6343,7 +6314,7 @@
       <c r="K196" s="26"/>
     </row>
     <row r="197" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="56">
+      <c r="A197" s="58">
         <v>2010</v>
       </c>
       <c r="B197" s="6">
@@ -6374,7 +6345,7 @@
       <c r="K197" s="26"/>
     </row>
     <row r="198" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="57"/>
+      <c r="A198" s="59"/>
       <c r="B198" s="10">
         <v>2</v>
       </c>
@@ -6403,7 +6374,7 @@
       <c r="K198" s="26"/>
     </row>
     <row r="199" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="58"/>
+      <c r="A199" s="60"/>
       <c r="B199" s="12">
         <v>3</v>
       </c>
@@ -6432,7 +6403,7 @@
       <c r="K199" s="26"/>
     </row>
     <row r="200" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="44">
+      <c r="A200" s="55">
         <v>2011</v>
       </c>
       <c r="B200" s="6">
@@ -6459,7 +6430,7 @@
       <c r="K200" s="26"/>
     </row>
     <row r="201" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="45"/>
+      <c r="A201" s="56"/>
       <c r="B201" s="10">
         <v>2</v>
       </c>
@@ -6484,7 +6455,7 @@
       <c r="K201" s="26"/>
     </row>
     <row r="202" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="46"/>
+      <c r="A202" s="57"/>
       <c r="B202" s="12">
         <v>3</v>
       </c>
@@ -6509,7 +6480,7 @@
       <c r="K202" s="26"/>
     </row>
     <row r="203" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="47">
+      <c r="A203" s="44">
         <v>2012</v>
       </c>
       <c r="B203" s="6">
@@ -6536,7 +6507,7 @@
       <c r="K203" s="26"/>
     </row>
     <row r="204" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="48"/>
+      <c r="A204" s="45"/>
       <c r="B204" s="10">
         <v>2</v>
       </c>
@@ -6561,7 +6532,7 @@
       <c r="K204" s="26"/>
     </row>
     <row r="205" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="49"/>
+      <c r="A205" s="46"/>
       <c r="B205" s="12">
         <v>3</v>
       </c>
@@ -6586,7 +6557,7 @@
       <c r="K205" s="26"/>
     </row>
     <row r="206" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="50">
+      <c r="A206" s="52">
         <v>2013</v>
       </c>
       <c r="B206" s="6">
@@ -6613,7 +6584,7 @@
       <c r="K206" s="26"/>
     </row>
     <row r="207" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="51"/>
+      <c r="A207" s="53"/>
       <c r="B207" s="10">
         <v>2</v>
       </c>
@@ -6638,7 +6609,7 @@
       <c r="K207" s="26"/>
     </row>
     <row r="208" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="52"/>
+      <c r="A208" s="54"/>
       <c r="B208" s="12">
         <v>3</v>
       </c>
@@ -6663,7 +6634,7 @@
       <c r="K208" s="26"/>
     </row>
     <row r="209" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="53">
+      <c r="A209" s="61">
         <v>2014</v>
       </c>
       <c r="B209" s="6">
@@ -6694,7 +6665,7 @@
       <c r="K209" s="26"/>
     </row>
     <row r="210" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="54"/>
+      <c r="A210" s="62"/>
       <c r="B210" s="10">
         <v>2</v>
       </c>
@@ -6723,7 +6694,7 @@
       <c r="K210" s="26"/>
     </row>
     <row r="211" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="55"/>
+      <c r="A211" s="63"/>
       <c r="B211" s="12">
         <v>3</v>
       </c>
@@ -6752,7 +6723,7 @@
       <c r="K211" s="26"/>
     </row>
     <row r="212" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="41">
+      <c r="A212" s="38">
         <v>2015</v>
       </c>
       <c r="B212" s="6">
@@ -6783,7 +6754,7 @@
       <c r="K212" s="26"/>
     </row>
     <row r="213" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="42"/>
+      <c r="A213" s="39"/>
       <c r="B213" s="10">
         <v>2</v>
       </c>
@@ -6812,7 +6783,7 @@
       <c r="K213" s="26"/>
     </row>
     <row r="214" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="43"/>
+      <c r="A214" s="40"/>
       <c r="B214" s="12">
         <v>3</v>
       </c>
@@ -6841,7 +6812,7 @@
       <c r="K214" s="28"/>
     </row>
     <row r="215" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="53">
+      <c r="A215" s="61">
         <v>2016</v>
       </c>
       <c r="B215" s="6">
@@ -6876,7 +6847,7 @@
       </c>
     </row>
     <row r="216" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="54"/>
+      <c r="A216" s="62"/>
       <c r="B216" s="10">
         <v>2</v>
       </c>
@@ -6909,7 +6880,7 @@
       </c>
     </row>
     <row r="217" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="55"/>
+      <c r="A217" s="63"/>
       <c r="B217" s="12">
         <v>3</v>
       </c>
@@ -6942,7 +6913,7 @@
       </c>
     </row>
     <row r="218" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="41">
+      <c r="A218" s="38">
         <v>2017</v>
       </c>
       <c r="B218" s="6">
@@ -6977,7 +6948,7 @@
       </c>
     </row>
     <row r="219" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="42"/>
+      <c r="A219" s="39"/>
       <c r="B219" s="10">
         <v>2</v>
       </c>
@@ -7010,7 +6981,7 @@
       </c>
     </row>
     <row r="220" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="43"/>
+      <c r="A220" s="40"/>
       <c r="B220" s="12">
         <v>3</v>
       </c>
@@ -7043,7 +7014,7 @@
       </c>
     </row>
     <row r="221" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A221" s="38">
+      <c r="A221" s="41">
         <v>2018</v>
       </c>
       <c r="B221" s="6">
@@ -7074,7 +7045,7 @@
       <c r="K221" s="16"/>
     </row>
     <row r="222" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="39"/>
+      <c r="A222" s="42"/>
       <c r="B222" s="10">
         <v>2</v>
       </c>
@@ -7103,7 +7074,7 @@
       <c r="K222" s="26"/>
     </row>
     <row r="223" spans="1:11" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="40"/>
+      <c r="A223" s="43"/>
       <c r="B223" s="12">
         <v>3</v>
       </c>
@@ -7132,7 +7103,7 @@
       <c r="K223" s="28"/>
     </row>
     <row r="224" spans="1:11" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="41">
+      <c r="A224" s="38">
         <v>2019</v>
       </c>
       <c r="B224" s="6">
@@ -7163,7 +7134,7 @@
       <c r="K224" s="11"/>
     </row>
     <row r="225" spans="1:11" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="42"/>
+      <c r="A225" s="39"/>
       <c r="B225" s="10">
         <v>2</v>
       </c>
@@ -7192,7 +7163,7 @@
       <c r="K225" s="26"/>
     </row>
     <row r="226" spans="1:11" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="43"/>
+      <c r="A226" s="40"/>
       <c r="B226" s="12">
         <v>3</v>
       </c>
@@ -7221,8 +7192,8 @@
       <c r="K226" s="28"/>
     </row>
     <row r="227" spans="1:11" s="4" customFormat="1" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="38" t="s">
-        <v>200</v>
+      <c r="A227" s="41">
+        <v>2020</v>
       </c>
       <c r="B227" s="6">
         <v>1</v>
@@ -7251,7 +7222,7 @@
       <c r="J227" s="31"/>
     </row>
     <row r="228" spans="1:11" s="4" customFormat="1" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="39"/>
+      <c r="A228" s="42"/>
       <c r="B228" s="10">
         <v>2</v>
       </c>
@@ -7279,7 +7250,7 @@
       <c r="J228" s="31"/>
     </row>
     <row r="229" spans="1:11" s="4" customFormat="1" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="40"/>
+      <c r="A229" s="43"/>
       <c r="B229" s="12">
         <v>3</v>
       </c>
@@ -7307,7 +7278,7 @@
       <c r="J229" s="31"/>
     </row>
     <row r="230" spans="1:11" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="41">
+      <c r="A230" s="38">
         <v>2021</v>
       </c>
       <c r="B230" s="36"/>
@@ -7318,10 +7289,10 @@
       <c r="K230" s="11"/>
     </row>
     <row r="231" spans="1:11" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="42"/>
+      <c r="A231" s="39"/>
       <c r="B231" s="36"/>
       <c r="C231" s="37" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D231" s="31"/>
       <c r="F231" s="31"/>
@@ -7330,7 +7301,7 @@
       <c r="K231" s="26"/>
     </row>
     <row r="232" spans="1:11" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="43"/>
+      <c r="A232" s="40"/>
       <c r="B232" s="36"/>
       <c r="D232" s="31"/>
       <c r="F232" s="31"/>
@@ -7338,7 +7309,7 @@
       <c r="J232" s="31"/>
     </row>
     <row r="233" spans="1:11" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="38">
+      <c r="A233" s="41">
         <v>2022</v>
       </c>
       <c r="B233" s="6">
@@ -7363,12 +7334,12 @@
         <v>1</v>
       </c>
       <c r="I233" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J233" s="31"/>
     </row>
     <row r="234" spans="1:11" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="39"/>
+      <c r="A234" s="42"/>
       <c r="B234" s="10">
         <v>2</v>
       </c>
@@ -7391,12 +7362,12 @@
         <v>2</v>
       </c>
       <c r="I234" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J234" s="31"/>
     </row>
     <row r="235" spans="1:11" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="40"/>
+      <c r="A235" s="43"/>
       <c r="B235" s="12">
         <v>3</v>
       </c>
@@ -7419,12 +7390,12 @@
         <v>3</v>
       </c>
       <c r="I235" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J235" s="31"/>
     </row>
     <row r="236" spans="1:11" s="4" customFormat="1" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="41">
+      <c r="A236" s="38">
         <v>2023</v>
       </c>
       <c r="B236" s="6">
@@ -7437,7 +7408,7 @@
         <v>1</v>
       </c>
       <c r="E236" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F236" s="6">
         <v>1</v>
@@ -7459,7 +7430,7 @@
       </c>
     </row>
     <row r="237" spans="1:11" s="4" customFormat="1" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="42"/>
+      <c r="A237" s="39"/>
       <c r="B237" s="10">
         <v>2</v>
       </c>
@@ -7482,17 +7453,17 @@
         <v>2</v>
       </c>
       <c r="I237" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="J237" s="10">
+        <v>2</v>
+      </c>
+      <c r="K237" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="J237" s="10">
-        <v>2</v>
-      </c>
-      <c r="K237" s="11" t="s">
-        <v>207</v>
-      </c>
     </row>
     <row r="238" spans="1:11" s="4" customFormat="1" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="43"/>
+      <c r="A238" s="40"/>
       <c r="B238" s="12">
         <v>3</v>
       </c>
@@ -7503,13 +7474,13 @@
         <v>3</v>
       </c>
       <c r="E238" s="15" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F238" s="12">
         <v>3</v>
       </c>
       <c r="G238" s="15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H238" s="12">
         <v>3</v>
@@ -7521,18 +7492,18 @@
         <v>3</v>
       </c>
       <c r="K238" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="239" spans="1:11" s="4" customFormat="1" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="38">
+      <c r="A239" s="41">
         <v>2024</v>
       </c>
       <c r="B239" s="6">
         <v>1</v>
       </c>
       <c r="C239" s="16" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D239" s="6">
         <v>1</v>
@@ -7544,13 +7515,13 @@
         <v>1</v>
       </c>
       <c r="G239" s="16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H239" s="6">
         <v>1</v>
       </c>
       <c r="I239" s="16" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J239" s="6">
         <v>1</v>
@@ -7560,7 +7531,7 @@
       </c>
     </row>
     <row r="240" spans="1:11" s="4" customFormat="1" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="39"/>
+      <c r="A240" s="42"/>
       <c r="B240" s="10">
         <v>2</v>
       </c>
@@ -7583,7 +7554,7 @@
         <v>2</v>
       </c>
       <c r="I240" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J240" s="10">
         <v>2</v>
@@ -7593,12 +7564,12 @@
       </c>
     </row>
     <row r="241" spans="1:11" s="4" customFormat="1" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="40"/>
+      <c r="A241" s="43"/>
       <c r="B241" s="12">
         <v>3</v>
       </c>
       <c r="C241" s="17" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D241" s="12">
         <v>3</v>
@@ -7616,17 +7587,17 @@
         <v>3</v>
       </c>
       <c r="I241" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J241" s="12">
         <v>3</v>
       </c>
       <c r="K241" s="17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="242" spans="1:11" s="4" customFormat="1" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="41">
+      <c r="A242" s="38">
         <v>2025</v>
       </c>
       <c r="B242" s="6">
@@ -7657,11 +7628,11 @@
         <v>1</v>
       </c>
       <c r="K242" s="16" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="243" spans="1:11" s="4" customFormat="1" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="42"/>
+      <c r="A243" s="39"/>
       <c r="B243" s="10">
         <v>2</v>
       </c>
@@ -7678,7 +7649,7 @@
         <v>2</v>
       </c>
       <c r="G243" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H243" s="10">
         <v>2</v>
@@ -7690,16 +7661,16 @@
         <v>2</v>
       </c>
       <c r="K243" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="244" spans="1:11" s="4" customFormat="1" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="43"/>
+      <c r="A244" s="40"/>
       <c r="B244" s="12">
         <v>3</v>
       </c>
       <c r="C244" s="17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D244" s="12">
         <v>3</v>
@@ -7727,7 +7698,7 @@
       </c>
     </row>
     <row r="245" spans="1:11" s="4" customFormat="1" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="41">
+      <c r="A245" s="38">
         <v>2026</v>
       </c>
       <c r="B245" s="6">
@@ -7740,7 +7711,7 @@
         <v>1</v>
       </c>
       <c r="E245" s="16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F245" s="6">
         <v>1</v>
@@ -7754,11 +7725,10 @@
       <c r="I245" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="J245" s="6"/>
-      <c r="K245" s="16"/>
+      <c r="J245" s="31"/>
     </row>
     <row r="246" spans="1:11" s="4" customFormat="1" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="42"/>
+      <c r="A246" s="39"/>
       <c r="B246" s="10">
         <v>2</v>
       </c>
@@ -7769,7 +7739,7 @@
         <v>2</v>
       </c>
       <c r="E246" s="14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F246" s="10">
         <v>2</v>
@@ -7781,13 +7751,12 @@
         <v>2</v>
       </c>
       <c r="I246" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="J246" s="6"/>
-      <c r="K246" s="14"/>
+        <v>202</v>
+      </c>
+      <c r="J246" s="31"/>
     </row>
     <row r="247" spans="1:11" s="4" customFormat="1" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="43"/>
+      <c r="A247" s="40"/>
       <c r="B247" s="12">
         <v>3</v>
       </c>
@@ -7804,7 +7773,7 @@
         <v>3</v>
       </c>
       <c r="G247" s="17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H247" s="12">
         <v>3</v>
@@ -7812,18 +7781,18 @@
       <c r="I247" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="J247" s="6"/>
-      <c r="K247" s="17"/>
-    </row>
-    <row r="248" spans="1:11" s="4" customFormat="1" ht="14.25" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="J247" s="31"/>
+    </row>
+    <row r="248" spans="1:11" s="4" customFormat="1" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="34"/>
       <c r="B248" s="31"/>
       <c r="D248" s="31"/>
       <c r="F248" s="31"/>
       <c r="H248" s="31"/>
-      <c r="J248" s="31"/>
-    </row>
-    <row r="249" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J248" s="25"/>
+      <c r="K248" s="11"/>
+    </row>
+    <row r="249" spans="1:11" s="4" customFormat="1" ht="14.25" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A249" s="34"/>
       <c r="B249" s="31"/>
       <c r="D249" s="31"/>
@@ -9633,11 +9602,67 @@
     </row>
   </sheetData>
   <mergeCells count="82">
-    <mergeCell ref="A245:A247"/>
-    <mergeCell ref="A242:A244"/>
-    <mergeCell ref="A239:A241"/>
-    <mergeCell ref="A236:A238"/>
-    <mergeCell ref="A233:A235"/>
+    <mergeCell ref="A227:A229"/>
+    <mergeCell ref="A221:A223"/>
+    <mergeCell ref="A218:A220"/>
+    <mergeCell ref="A200:A202"/>
+    <mergeCell ref="A203:A205"/>
+    <mergeCell ref="A206:A208"/>
+    <mergeCell ref="A209:A211"/>
+    <mergeCell ref="A212:A214"/>
+    <mergeCell ref="A215:A217"/>
+    <mergeCell ref="A224:A226"/>
+    <mergeCell ref="A197:A199"/>
+    <mergeCell ref="A164:A166"/>
+    <mergeCell ref="A167:A169"/>
+    <mergeCell ref="A170:A172"/>
+    <mergeCell ref="A173:A175"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A179:A181"/>
+    <mergeCell ref="A182:A184"/>
+    <mergeCell ref="A185:A187"/>
+    <mergeCell ref="A188:A190"/>
+    <mergeCell ref="A191:A193"/>
+    <mergeCell ref="A194:A196"/>
+    <mergeCell ref="A119:A121"/>
+    <mergeCell ref="A122:A124"/>
+    <mergeCell ref="A161:A163"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="A131:A133"/>
+    <mergeCell ref="A134:A136"/>
+    <mergeCell ref="A137:A139"/>
+    <mergeCell ref="A140:A142"/>
+    <mergeCell ref="A143:A145"/>
+    <mergeCell ref="A146:A148"/>
+    <mergeCell ref="A149:A151"/>
+    <mergeCell ref="A152:A154"/>
+    <mergeCell ref="A155:A157"/>
+    <mergeCell ref="A158:A160"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A32:A34"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A62:A64"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="A86:A88"/>
     <mergeCell ref="A230:A232"/>
     <mergeCell ref="A35:A37"/>
     <mergeCell ref="A38:A40"/>
@@ -9654,67 +9679,11 @@
     <mergeCell ref="A113:A115"/>
     <mergeCell ref="A116:A118"/>
     <mergeCell ref="A44:A46"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="A56:A58"/>
-    <mergeCell ref="A59:A61"/>
-    <mergeCell ref="A62:A64"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A29:A31"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A119:A121"/>
-    <mergeCell ref="A122:A124"/>
-    <mergeCell ref="A161:A163"/>
-    <mergeCell ref="A128:A130"/>
-    <mergeCell ref="A131:A133"/>
-    <mergeCell ref="A134:A136"/>
-    <mergeCell ref="A137:A139"/>
-    <mergeCell ref="A140:A142"/>
-    <mergeCell ref="A143:A145"/>
-    <mergeCell ref="A146:A148"/>
-    <mergeCell ref="A149:A151"/>
-    <mergeCell ref="A152:A154"/>
-    <mergeCell ref="A155:A157"/>
-    <mergeCell ref="A158:A160"/>
-    <mergeCell ref="A197:A199"/>
-    <mergeCell ref="A164:A166"/>
-    <mergeCell ref="A167:A169"/>
-    <mergeCell ref="A170:A172"/>
-    <mergeCell ref="A173:A175"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A181"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A185:A187"/>
-    <mergeCell ref="A188:A190"/>
-    <mergeCell ref="A191:A193"/>
-    <mergeCell ref="A194:A196"/>
-    <mergeCell ref="A227:A229"/>
-    <mergeCell ref="A221:A223"/>
-    <mergeCell ref="A218:A220"/>
-    <mergeCell ref="A200:A202"/>
-    <mergeCell ref="A203:A205"/>
-    <mergeCell ref="A206:A208"/>
-    <mergeCell ref="A209:A211"/>
-    <mergeCell ref="A212:A214"/>
-    <mergeCell ref="A215:A217"/>
-    <mergeCell ref="A224:A226"/>
+    <mergeCell ref="A245:A247"/>
+    <mergeCell ref="A242:A244"/>
+    <mergeCell ref="A239:A241"/>
+    <mergeCell ref="A236:A238"/>
+    <mergeCell ref="A233:A235"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
